--- a/results/ncbc_s13/TM_m3/reference_peaks.xlsx
+++ b/results/ncbc_s13/TM_m3/reference_peaks.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,17 +417,17 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>step_id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>side</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>peak_value</t>
         </is>
@@ -468,7 +456,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.7279879037174464</v>
+        <v>0.7279879037174465</v>
       </c>
     </row>
     <row r="4">
@@ -533,7 +521,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.9479172706966271</v>
+        <v>0.9479172706966269</v>
       </c>
     </row>
     <row r="9">
@@ -754,7 +742,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1.116051493666026</v>
+        <v>1.116051493666025</v>
       </c>
     </row>
     <row r="26">
@@ -767,7 +755,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1.114898080969676</v>
+        <v>1.114898080969677</v>
       </c>
     </row>
     <row r="27">
@@ -1118,7 +1106,7 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>1.096192654429493</v>
+        <v>1.096192654429492</v>
       </c>
     </row>
     <row r="54">
@@ -1872,7 +1860,7 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>1.067597263198157</v>
+        <v>1.067597263198156</v>
       </c>
     </row>
     <row r="112">
@@ -2119,7 +2107,7 @@
         </is>
       </c>
       <c r="C130" t="n">
-        <v>1.101620422435082</v>
+        <v>1.101620422435081</v>
       </c>
     </row>
     <row r="131">
@@ -2392,7 +2380,7 @@
         </is>
       </c>
       <c r="C151" t="n">
-        <v>0.9768111708897637</v>
+        <v>0.9768111708897634</v>
       </c>
     </row>
     <row r="152">
@@ -3432,7 +3420,7 @@
         </is>
       </c>
       <c r="C231" t="n">
-        <v>0.950043192030953</v>
+        <v>0.9500431920309529</v>
       </c>
     </row>
     <row r="232">
@@ -4082,7 +4070,7 @@
         </is>
       </c>
       <c r="C281" t="n">
-        <v>1.097488173673666</v>
+        <v>1.097488173673667</v>
       </c>
     </row>
     <row r="282">
